--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_o_higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:30</t>
+    <t xml:space="preserve">2026-09-24 01:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -993,13 +993,13 @@
         <v>-0.82</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.07</v>
@@ -1013,19 +1013,19 @@
         <v>29</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="22">
@@ -1036,16 +1036,16 @@
         <v>29</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>-0.64</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.23</v>
@@ -1059,19 +1059,19 @@
         <v>29</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.84</v>
+        <v>-0.82</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>-0.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="24">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_o_higgins.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:20</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_o_higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
